--- a/backend/app/app_tasks/resource/product_temp.xlsx
+++ b/backend/app/app_tasks/resource/product_temp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wondron\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\47202\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC23C886-2570-450D-A7B6-AD8EC3BC636D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC9FADB-1901-4625-BA8F-7407762FA2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12960" windowHeight="19740" xr2:uid="{3431217A-AB0B-449F-83A2-0B552DC9433A}"/>
+    <workbookView xWindow="38280" yWindow="1080" windowWidth="29040" windowHeight="15720" xr2:uid="{3431217A-AB0B-449F-83A2-0B552DC9433A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="88">
   <si>
     <t>大类目</t>
   </si>
@@ -256,6 +256,50 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t>材料1用量单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料2用量单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料3用量单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料10用量单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料9用量单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料8用量单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料7用量单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料6用量单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料5用量单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料4用量单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -331,18 +375,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -658,10 +705,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F059B201-0E2F-4A35-B300-1B2E0E1A8361}">
-  <dimension ref="A1:AV3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BF3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="31" max="31" width="15.83203125" customWidth="1"/>
+    <col min="34" max="34" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.5" customWidth="1"/>
+    <col min="42" max="42" width="9" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="10" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="15.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -753,311 +815,381 @@
         <v>29</v>
       </c>
       <c r="AE1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AO1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AU1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="BA1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="BD1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="BF1" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="2" spans="1:48" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:58" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="3">
         <v>2980</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="3">
         <v>43</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="3">
         <v>0.85</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="3">
         <v>20</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="3">
         <v>65</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U2" s="3">
         <v>53</v>
       </c>
-      <c r="V2" s="2">
+      <c r="V2" s="3">
         <v>38</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="Y2" s="2">
+      <c r="Y2" s="3">
         <v>6108320000</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="AA2" s="2">
+      <c r="AA2" s="3">
         <v>860</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AD2" s="2">
+      <c r="AD2" s="3">
         <v>0.95</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AE2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF2" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="AF2" s="2">
+      <c r="AG2" s="3">
         <v>1</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AH2" s="2">
+      <c r="AJ2" s="3">
         <v>5</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AK2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AJ2" s="2">
+      <c r="AM2" s="3">
         <v>1</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AN2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="AL2" s="2">
+      <c r="AP2" s="3">
         <v>1</v>
       </c>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
-      <c r="AR2" s="2"/>
-      <c r="AS2" s="2"/>
-      <c r="AT2" s="2"/>
-      <c r="AU2" s="2"/>
-      <c r="AV2" s="2"/>
+      <c r="AQ2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR2" s="3"/>
+      <c r="AS2" s="3"/>
+      <c r="AT2" s="3"/>
+      <c r="AU2" s="3"/>
+      <c r="AV2" s="3"/>
+      <c r="AW2" s="3"/>
+      <c r="AX2" s="3"/>
+      <c r="AY2" s="3"/>
+      <c r="AZ2" s="3"/>
+      <c r="BA2" s="3"/>
+      <c r="BB2" s="3"/>
+      <c r="BC2" s="3"/>
+      <c r="BD2" s="3"/>
+      <c r="BE2" s="3"/>
+      <c r="BF2" s="3"/>
     </row>
-    <row r="3" spans="1:48" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:58" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="3">
         <v>2980</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="3">
         <v>43</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="3">
         <v>0.85</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="3">
         <v>20</v>
       </c>
-      <c r="T3" s="2">
+      <c r="T3" s="3">
         <v>65</v>
       </c>
-      <c r="U3" s="2">
+      <c r="U3" s="3">
         <v>53</v>
       </c>
-      <c r="V3" s="2">
+      <c r="V3" s="3">
         <v>38</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="Y3" s="2">
+      <c r="Y3" s="3">
         <v>6108320000</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="AA3" s="2">
+      <c r="AA3" s="3">
         <v>860</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AB3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AC3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AD3" s="2">
+      <c r="AD3" s="3">
         <v>0.95</v>
       </c>
-      <c r="AE3" s="2" t="s">
+      <c r="AE3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="AF3" s="2">
+      <c r="AG3" s="3">
         <v>1</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AH3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI3" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AH3" s="2">
+      <c r="AJ3" s="3">
         <v>5</v>
       </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AK3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AJ3" s="2">
+      <c r="AM3" s="3">
         <v>1</v>
       </c>
-      <c r="AK3" s="2" t="s">
+      <c r="AN3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="AL3" s="2">
+      <c r="AP3" s="3">
         <v>1</v>
       </c>
-      <c r="AM3" s="2"/>
-      <c r="AN3" s="2"/>
-      <c r="AO3" s="2"/>
-      <c r="AP3" s="2"/>
-      <c r="AQ3" s="2"/>
-      <c r="AR3" s="2"/>
-      <c r="AS3" s="2"/>
-      <c r="AT3" s="2"/>
-      <c r="AU3" s="2"/>
-      <c r="AV3" s="2"/>
+      <c r="AQ3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR3" s="3"/>
+      <c r="AS3" s="3"/>
+      <c r="AT3" s="3"/>
+      <c r="AU3" s="3"/>
+      <c r="AV3" s="3"/>
+      <c r="AW3" s="3"/>
+      <c r="AX3" s="3"/>
+      <c r="AY3" s="3"/>
+      <c r="AZ3" s="3"/>
+      <c r="BA3" s="3"/>
+      <c r="BB3" s="3"/>
+      <c r="BC3" s="3"/>
+      <c r="BD3" s="3"/>
+      <c r="BE3" s="3"/>
+      <c r="BF3" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
